--- a/public/sap-reporting/expansion-150-downloads/EXT-FI26-01.xlsx
+++ b/public/sap-reporting/expansion-150-downloads/EXT-FI26-01.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="R6d3c9faa5f204d34"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="R1fc7e93a40654445"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="R1bcab6e74e35447d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="R1154e2172ef1463e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="R2fd1178fadd34551"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="Rb5de158bf69f4fab"/>
   </x:sheets>
 </x:workbook>
 </file>
